--- a/out/Attention-MambaAMT_repeat_3_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.305315212968727</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.305315212968727</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.905315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.905315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9209439647931161</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.905315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.905315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.905315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.905315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.905315212968727</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.3648012947504813</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001995408792593516</v>
+        <v>-0.0003477053636671044</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.300411634876904</v>
+        <v>4.00852923952581</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.604379290988927</v>
+        <v>8.023255093397129</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.344956986269922</v>
+        <v>0.6010968406163874</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.990794159816257</v>
+        <v>5.211539431398076</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4313084178413344</v>
+        <v>0.7515666350338622</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.508508904380521</v>
+        <v>6.113671387422584</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.618278571537797</v>
+        <v>1.077367369765106</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.305315212968727</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.314001248231842</v>
+        <v>7.517263520818768</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6614356030588884</v>
+        <v>1.152569680951635</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.018640351877662</v>
+        <v>8.745115839531424</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7009891584686315</v>
+        <v>1.221491550630056</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.759232420514189</v>
+        <v>10.03561647477575</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3163433696774869</v>
+        <v>0.5512357526905476</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.690347482194872</v>
+        <v>9.915582707636711</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1527793885929284</v>
+        <v>0.2662216734698266</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.67931483327514</v>
+        <v>9.896358012264306</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07279483013258747</v>
+        <v>0.126847314380164</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.672003776931756</v>
+        <v>9.883618263291044</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02156860039030227</v>
+        <v>0.03758397443150337</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.64226860733183</v>
+        <v>9.831803781417545</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01426568925414641</v>
+        <v>0.02485991708285228</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.649221740406394</v>
+        <v>9.843920978701385</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007298898836720305</v>
+        <v>0.01272245944402225</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.649545384312137</v>
+        <v>9.84448864253128</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003731729854252433</v>
+        <v>0.006506090705092871</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.649704615765521</v>
+        <v>9.84476980875986</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001399778406291622</v>
+        <v>0.002442765822169778</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.648769611752348</v>
+        <v>9.843144316853286</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007606055468959831</v>
+        <v>0.00132903466522716</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.648890261877042</v>
+        <v>9.843358256779609</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003637546970590644</v>
+        <v>0.0006371418000511294</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.648856681614162</v>
+        <v>9.843303457388744</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002232775872449294</v>
+        <v>0.0003925178674437563</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.648939309658065</v>
+        <v>9.843451240503915</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001144068222683124</v>
+        <v>0.0002029325698120612</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.648944713084244</v>
+        <v>9.843464402283621</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.294740158554031e-05</v>
+        <v>9.590840620930295e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.648936126310618</v>
+        <v>9.843453126037835</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.209524495511864e-05</v>
+        <v>6.02364652658983e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.648947343888983</v>
+        <v>9.843476646606684</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.131855788691358e-05</v>
+        <v>2.41402819409171e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.648939027588745</v>
+        <v>9.8434658139553</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>8.38179904731087e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.648931972734164</v>
+        <v>9.843457251121864</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>1.675769385467227e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.64892763419689</v>
+        <v>9.843453326675055</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.648922055901767</v>
+        <v>9.843447315248465</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.6489170092807</v>
+        <v>9.843442222006331</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.648917327560915</v>
+        <v>9.843437857032363</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.648918418807373</v>
+        <v>9.843438948278818</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.648917729200236</v>
+        <v>9.843438258671682</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.648917759512639</v>
+        <v>9.843438288984084</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.648917570060128</v>
+        <v>9.843438099531575</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.648917623106832</v>
+        <v>9.843438152578278</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.648917676153534</v>
+        <v>9.843438205624979</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.648917638263032</v>
+        <v>9.843438167734478</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.648917509435325</v>
+        <v>9.843438038906772</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.648917365451418</v>
+        <v>9.843437894922864</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.648917206311309</v>
+        <v>9.843437735782755</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.648917259358012</v>
+        <v>9.843437788829458</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.648917206311309</v>
+        <v>9.843437735782755</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.648917206311309</v>
+        <v>9.843437735782755</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.6489170244369</v>
+        <v>9.843437553908347</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.648917191155109</v>
+        <v>9.843437720626556</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.648917388185719</v>
+        <v>9.843437917657164</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.648917229045611</v>
+        <v>9.843437758517057</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.648917266936112</v>
+        <v>9.843437796407558</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.648917463966723</v>
+        <v>9.843437993438169</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.648917441232421</v>
+        <v>9.843437970703869</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.648917289670413</v>
+        <v>9.84343781914186</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.64891721388941</v>
+        <v>9.843437743360857</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.648917312404715</v>
+        <v>9.84343784187616</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.648917319982815</v>
+        <v>9.843437849454261</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.64891758521633</v>
+        <v>9.843438114687775</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.648917289670413</v>
+        <v>9.84343781914186</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.648917532169626</v>
+        <v>9.843438061641073</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.648917615528731</v>
+        <v>9.843438145000176</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.648917448810522</v>
+        <v>9.843437978281967</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.648917638263032</v>
+        <v>9.843438167734478</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.648917289670413</v>
+        <v>9.84343781914186</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.648917085061703</v>
+        <v>9.843437614533149</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.648917198733209</v>
+        <v>9.843437728204654</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.64891721388941</v>
+        <v>9.843437743360857</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.648916978968298</v>
+        <v>9.843437508439743</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.6489170395931</v>
+        <v>9.843437569064546</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.648916910765394</v>
+        <v>9.843437440236841</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.648917047171201</v>
+        <v>9.843437576642648</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.64891722146751</v>
+        <v>9.843437750938955</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.648917365451418</v>
+        <v>9.843437894922864</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.648917198733209</v>
+        <v>9.843437728204654</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.648917191155109</v>
+        <v>9.843437720626556</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.648916903187294</v>
+        <v>9.843437432658739</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.648916918343494</v>
+        <v>9.843437447814939</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.648917145686506</v>
+        <v>9.843437675157952</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.648917130530306</v>
+        <v>9.843437660001751</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.648917236623711</v>
+        <v>9.843437766095157</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.648916963812097</v>
+        <v>9.843437493283542</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.648917062327402</v>
+        <v>9.843437591798848</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.64891721388941</v>
+        <v>9.843437743360857</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.648917229045611</v>
+        <v>9.843437758517057</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.648917206311309</v>
+        <v>9.843437735782755</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.648917289670413</v>
+        <v>9.84343781914186</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.648917388185719</v>
+        <v>9.843437917657164</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.64891722146751</v>
+        <v>9.843437750938955</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.648917206311309</v>
+        <v>9.843437735782755</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.648917175998908</v>
+        <v>9.843437705470354</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.648917160842707</v>
+        <v>9.843437690314154</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.648917198733209</v>
+        <v>9.843437728204654</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.64891721388941</v>
+        <v>9.843437743360857</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.648917206311309</v>
+        <v>9.843437735782755</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9209439647931161</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.305315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001995408792593516</v>
+        <v>-0.000180893663955736</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.300411634876904</v>
+        <v>2.085436782596542</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.604379290988927</v>
+        <v>4.174097274102817</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.344956986269922</v>
+        <v>0.3127205255255465</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.990794159816257</v>
+        <v>2.711302644967966</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4313084178413344</v>
+        <v>0.3910024663261842</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.508508904380521</v>
+        <v>3.180636668921612</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.618278571537797</v>
+        <v>0.5605000185129196</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.314001248231842</v>
+        <v>3.910855225223184</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6614356030588884</v>
+        <v>0.5996243441455187</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.018640351877662</v>
+        <v>4.549645359549583</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7009891584686315</v>
+        <v>0.6354802071634201</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.305315212968727</v>
+        <v>0.4147854768329917</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.759232420514189</v>
+        <v>5.221028279910265</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3163433696774869</v>
+        <v>0.2867803983396693</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.690347482194872</v>
+        <v>5.158580643914885</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1527793885929284</v>
+        <v>0.1385024678204155</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.67931483327514</v>
+        <v>5.148578973427445</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07279483013258747</v>
+        <v>0.06599168953992489</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.672003776931756</v>
+        <v>5.141951121247352</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02156860039030227</v>
+        <v>0.01955287728778354</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.64226860733183</v>
+        <v>5.114994392510542</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01426568925414641</v>
+        <v>0.01293243814303897</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.649221740406394</v>
+        <v>5.121297478115158</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007298898836720305</v>
+        <v>0.006617017940337822</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.649545384312137</v>
+        <v>5.121590419713407</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003731729854252433</v>
+        <v>0.003382418092553728</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.649704615765521</v>
+        <v>5.121734298711424</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001399778406291622</v>
+        <v>0.001268080430701783</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.648769611752348</v>
+        <v>5.120886232497172</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007606055468959831</v>
+        <v>0.0006888300268744847</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.648890261877042</v>
+        <v>5.120995171125579</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003637546970590644</v>
+        <v>0.0003295813091850563</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.648856681614162</v>
+        <v>5.120964239464647</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002232775872449294</v>
+        <v>0.0002016305746613585</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.03121662094114408</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.648939309658065</v>
+        <v>5.121038747405173</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001144068222683124</v>
+        <v>0.0001030837615359724</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329917</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.648944713084244</v>
+        <v>5.121043209768161</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.294740158554031e-05</v>
+        <v>4.795193593161442e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.648936126310618</v>
+        <v>5.121034932199159</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.209524495511864e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.648947343888983</v>
+        <v>5.121044752486718</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.131855788691358e-05</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.648939027588745</v>
+        <v>5.121036664945675</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.648931972734164</v>
+        <v>5.121029746496901</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.64892763419689</v>
+        <v>5.121025325953051</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.648922055901767</v>
+        <v>5.121019747657927</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329917</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.6489170092807</v>
+        <v>5.121014701036859</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.648917327560915</v>
+        <v>5.121015019317076</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.648918418807373</v>
+        <v>5.121016110563533</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.648917729200236</v>
+        <v>5.121015420956397</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.648917759512639</v>
+        <v>5.121015451268799</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.648917570060128</v>
+        <v>5.121015261816289</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.648917623106832</v>
+        <v>5.121015314862992</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.648917676153534</v>
+        <v>5.121015367909694</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.648917638263032</v>
+        <v>5.121015330019191</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.648917509435325</v>
+        <v>5.121015201191485</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.648917365451418</v>
+        <v>5.121015057207578</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.648917206311309</v>
+        <v>5.12101489806747</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.648917259358012</v>
+        <v>5.121014951114172</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.648917206311309</v>
+        <v>5.12101489806747</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.648917206311309</v>
+        <v>5.12101489806747</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.6489170244369</v>
+        <v>5.12101471619306</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.648917191155109</v>
+        <v>5.121014882911268</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.648917388185719</v>
+        <v>5.121015079941879</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.648917229045611</v>
+        <v>5.121014920801771</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.648917266936112</v>
+        <v>5.121014958692272</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.648917463966723</v>
+        <v>5.121015155722882</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.648917441232421</v>
+        <v>5.121015132988582</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.648917289670413</v>
+        <v>5.121014981426574</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.64891721388941</v>
+        <v>5.12101490564557</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.648917312404715</v>
+        <v>5.121015004160875</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.648917319982815</v>
+        <v>5.121015011738976</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.64891758521633</v>
+        <v>5.121015276972489</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.648917289670413</v>
+        <v>5.121014981426574</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.648917532169626</v>
+        <v>5.121015223925786</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9209439647931161</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.648917615528731</v>
+        <v>5.121015307284891</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.03121662094114397</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.648917448810522</v>
+        <v>5.121015140566683</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114397</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.648917638263032</v>
+        <v>5.121015330019191</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.648917289670413</v>
+        <v>5.121014981426574</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.648917085061703</v>
+        <v>5.121014776817863</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.648917198733209</v>
+        <v>5.121014890489369</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.64891721388941</v>
+        <v>5.12101490564557</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.648916978968298</v>
+        <v>5.121014670724458</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.231216620941144</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.6489170395931</v>
+        <v>5.121014731349261</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.03121662094114394</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.648916910765394</v>
+        <v>5.121014602521553</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114394</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.648917047171201</v>
+        <v>5.121014738927362</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.64891722146751</v>
+        <v>5.12101491322367</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.648917365451418</v>
+        <v>5.121015057207578</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.648917198733209</v>
+        <v>5.121014890489369</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.648917191155109</v>
+        <v>5.121014882911268</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.231216620941144</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.648916903187294</v>
+        <v>5.121014594943453</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.648916918343494</v>
+        <v>5.121014610099655</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329918</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.648917145686506</v>
+        <v>5.121014837442666</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.648917130530306</v>
+        <v>5.121014822286465</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.648917236623711</v>
+        <v>5.121014928379871</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.648916963812097</v>
+        <v>5.121014655568257</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.648917062327402</v>
+        <v>5.121014754083562</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.64891721388941</v>
+        <v>5.12101490564557</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.648917229045611</v>
+        <v>5.121014920801771</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.648917206311309</v>
+        <v>5.12101489806747</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.648917289670413</v>
+        <v>5.121014981426574</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.648917388185719</v>
+        <v>5.121015079941879</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.64891722146751</v>
+        <v>5.12101491322367</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.648917206311309</v>
+        <v>5.12101489806747</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.648917175998908</v>
+        <v>5.121014867755068</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.648917160842707</v>
+        <v>5.121014852598868</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.648917198733209</v>
+        <v>5.121014890489369</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.64891721388941</v>
+        <v>5.12101490564557</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.648917206311309</v>
+        <v>5.12101489806747</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.001069243997335434</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.060787574607127</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01142231002449989</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.060787574607127</v>
+        <v>0.04999999999999971</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01071396470069885</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.260787574607127</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.005626291036605835</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01335504651069641</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.003568701446056366</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.001279283314943314</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.260787574607127</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.004034630954265594</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.260787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.002984914928674698</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.260787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.004621114581823349</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.260787574607127</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01007644087076187</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.260787574607127</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001906268298625946</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01176420226693153</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.00311705470085144</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.260787574607127</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.007739096879959106</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.260787574607127</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.004563454538583755</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.060787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.006366092711687088</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002147499471902847</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0025893934071064</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.007094211876392365</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01222530379891396</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01978583261370659</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.002570811659097672</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.004907354712486267</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.060787574607127</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.007854923605918884</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.060787574607127</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.010359738022089</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.060787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.00861290842294693</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.060787574607127</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.02060628309845924</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.060787574607127</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0106029286980629</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.060787574607127</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01276631653308868</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.060787574607127</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01359903812408447</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.060787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.005931396037340164</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.060787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.007702503353357315</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01168807223439217</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.02718499861657619</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.060787574607127</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01284054294228554</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.060787574607127</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.009879015386104584</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.060787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01077662780880928</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000180893663955736</v>
+        <v>-7.712256331345998e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.085436782596542</v>
+        <v>0.889109252280405</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.006032917648553848</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.174097274102817</v>
+        <v>1.779592907008404</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3127205255255465</v>
+        <v>0.1333258984963202</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002121344208717346</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.711302644967966</v>
+        <v>1.155942144807108</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3910024663261842</v>
+        <v>0.1667007545622656</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01787970215082169</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.180636668921612</v>
+        <v>1.356038928517799</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5605000185129196</v>
+        <v>0.2389645784281521</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01511580497026443</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.910855225223184</v>
+        <v>1.667361733030028</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5996243441455187</v>
+        <v>0.2556451129256772</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01221316307783127</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.549645359549583</v>
+        <v>1.939704871897068</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6354802071634201</v>
+        <v>0.2709315542955592</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.007417406886816025</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4147854768329917</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.221028279910265</v>
+        <v>2.225943688836998</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2867803983396693</v>
+        <v>0.1222670373213373</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.003257028758525848</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2312166209411441</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.158580643914885</v>
+        <v>2.19931958941948</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1385024678204155</v>
+        <v>0.05904874746033055</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.024882473051548</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.148578973427445</v>
+        <v>2.19505546025556</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06599168953992489</v>
+        <v>0.02813558306727647</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01477105915546417</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.141951121247352</v>
+        <v>2.192229698691393</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01955287728778354</v>
+        <v>0.008333563627179606</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01671317964792252</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.114994392510542</v>
+        <v>2.180734450292196</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01293243814303897</v>
+        <v>0.005510641582937633</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01549462229013443</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.121297478115158</v>
+        <v>2.18341892269172</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006617017940337822</v>
+        <v>0.002817967231921131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01415617018938065</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.121590419713407</v>
+        <v>2.183540957973626</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003382418092553728</v>
+        <v>0.001439560167255453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01209438592195511</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.121734298711424</v>
+        <v>2.183599447234295</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001268080430701783</v>
+        <v>0.0005376864856202011</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01361658424139023</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.120886232497172</v>
+        <v>2.183234922977324</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006888300268744847</v>
+        <v>0.0002911771458358382</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.02011410892009735</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.120995171125579</v>
+        <v>2.183278531161338</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003295813091850563</v>
+        <v>0.0001372566611499408</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.009281165897846222</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.120964239464647</v>
+        <v>2.183262475273386</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002016305746613585</v>
+        <v>8.355596056915365e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0176045224070549</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.03121662094114408</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.121038747405173</v>
+        <v>2.183291468911106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001030837615359724</v>
+        <v>4.132161208684532e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01446893066167831</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6147854768329917</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.121043209768161</v>
+        <v>2.183290504722986</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.795193593161442e-05</v>
+        <v>1.698004887727391e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.006519850343465805</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.121034932199159</v>
+        <v>2.183284113910244</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.82578058218305e-05</v>
+        <v>9.070610155389825e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0196322426199913</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.121044752486718</v>
+        <v>2.1832855457952</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.015294660927689e-05</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.03100252151489258</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6772187187152797</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.121036664945675</v>
+        <v>2.18327917324003</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01664798706769943</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.121029746496901</v>
+        <v>2.183273351047698</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-1.662115307266386e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01561442762613297</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.121025325953051</v>
+        <v>2.183268599772485</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.007022004574537277</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2312166209411441</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.121019747657927</v>
+        <v>2.183263310624922</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.006369102746248245</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.6147854768329917</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.121014701036859</v>
+        <v>2.183263287890621</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01828261837363243</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.260787574607127</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.121015019317076</v>
+        <v>2.183263606170838</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.008111841976642609</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.121016110563533</v>
+        <v>2.183264697417295</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01062045991420746</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.121015420956397</v>
+        <v>2.183264007810159</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02191146463155746</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.121015451268799</v>
+        <v>2.183264038122561</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02214118838310242</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.121015261816289</v>
+        <v>2.18326384867005</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01741078495979309</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.121015314862992</v>
+        <v>2.183263901716753</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01835012435913086</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.121015367909694</v>
+        <v>2.183263954763456</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01526471227407455</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.121015330019191</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01901755481958389</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.121015201191485</v>
+        <v>2.183263788045247</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01955351978540421</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.121015057207578</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01517894119024277</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.12101489806747</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02347294241189957</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.121014951114172</v>
+        <v>2.183263537967934</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003042057156562805</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.12101489806747</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01277055591344833</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.12101489806747</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0001972652971744537</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.12101471619306</v>
+        <v>2.183263303046822</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.007692523300647736</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.121014882911268</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01070556789636612</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.121015079941879</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00463973730802536</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.121014920801771</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>6.627291440963745e-06</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.121014958692272</v>
+        <v>2.183263545546035</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0005491189658641815</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.121015155722882</v>
+        <v>2.183263742576645</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01444820314645767</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6772187187152797</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.121015132988582</v>
+        <v>2.183263719842344</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01271627098321915</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6772187187152797</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.121014981426574</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.004664823412895203</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.12101490564557</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.002004604786634445</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.121015004160875</v>
+        <v>2.183263591014637</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003692936152219772</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.121015011738976</v>
+        <v>2.183263598592738</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01047768443822861</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.121015276972489</v>
+        <v>2.183263863826252</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.001770868897438049</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2312166209411441</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.121014981426574</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0001426562666893005</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.121015223925786</v>
+        <v>2.183263810779549</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0007001534104347229</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.121015307284891</v>
+        <v>2.183263894138653</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.003066603094339371</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.03121662094114397</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.121015140566683</v>
+        <v>2.183263727420444</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02072389423847198</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.03121662094114397</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.121015330019191</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01871169358491898</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6772187187152797</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.121014981426574</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01558264344930649</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.121014776817863</v>
+        <v>2.183263363671625</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.002620015293359756</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.121014890489369</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01234301179647446</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.12101490564557</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.004158694297075272</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.121014670724458</v>
+        <v>2.18326325757822</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01479200273752213</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.231216620941144</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.121014731349261</v>
+        <v>2.183263318203023</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.007521037012338638</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.03121662094114394</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.121014602521553</v>
+        <v>2.183263189375316</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003229990601539612</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.03121662094114394</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.121014738927362</v>
+        <v>2.183263325781123</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01075168699026108</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6772187187152797</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.12101491322367</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.00791342556476593</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6772187187152797</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.121015057207578</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01106015592813492</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.121014890489369</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02075358480215073</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.121014882911268</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.006201490759849548</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.231216620941144</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.121014594943453</v>
+        <v>2.183263181797216</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.003427926450967789</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.121014610099655</v>
+        <v>2.183263196953417</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.003295600414276123</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6147854768329918</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.121014837442666</v>
+        <v>2.183263424296428</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002821318805217743</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.121014822286465</v>
+        <v>2.183263409140228</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01525280624628067</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6772187187152797</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.121014928379871</v>
+        <v>2.183263515233633</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.001255214214324951</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.121014655568257</v>
+        <v>2.183263242422019</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.0003103949129581451</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.121014754083562</v>
+        <v>2.183263340937324</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.006727207452058792</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.12101490564557</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.005261402577161789</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.121014920801771</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005643010139465332</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.12101489806747</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.007081016898155212</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.121014981426574</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.009387202560901642</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.121015079941879</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.009071685373783112</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.12101491322367</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.009486831724643707</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.12101489806747</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.008332453668117523</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.121014867755068</v>
+        <v>2.18326345460883</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01113899797201157</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.121014852598868</v>
+        <v>2.183263439452629</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001903451979160309</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.121014890489369</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003851063549518585</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.3000000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.12101490564557</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01805855333805084</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.4400000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.12101489806747</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
   </sheetData>
